--- a/artfynd/A 29274-2026 artfynd.xlsx
+++ b/artfynd/A 29274-2026 artfynd.xlsx
@@ -1848,7 +1848,7 @@
         <v>136583208</v>
       </c>
       <c r="B12" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>136583209</v>
       </c>
       <c r="B68" t="n">
-        <v>100368</v>
+        <v>100371</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>136583210</v>
       </c>
       <c r="B69" t="n">
-        <v>100368</v>
+        <v>100371</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 29274-2026 artfynd.xlsx
+++ b/artfynd/A 29274-2026 artfynd.xlsx
@@ -1848,7 +1848,7 @@
         <v>136583208</v>
       </c>
       <c r="B12" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>136583209</v>
       </c>
       <c r="B68" t="n">
-        <v>100371</v>
+        <v>100372</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>136583210</v>
       </c>
       <c r="B69" t="n">
-        <v>100371</v>
+        <v>100372</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 29274-2026 artfynd.xlsx
+++ b/artfynd/A 29274-2026 artfynd.xlsx
@@ -1848,7 +1848,7 @@
         <v>136583208</v>
       </c>
       <c r="B12" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>136583209</v>
       </c>
       <c r="B68" t="n">
-        <v>100372</v>
+        <v>100377</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>136583210</v>
       </c>
       <c r="B69" t="n">
-        <v>100372</v>
+        <v>100377</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 29274-2026 artfynd.xlsx
+++ b/artfynd/A 29274-2026 artfynd.xlsx
@@ -1848,7 +1848,7 @@
         <v>136583208</v>
       </c>
       <c r="B12" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>136583209</v>
       </c>
       <c r="B68" t="n">
-        <v>100377</v>
+        <v>100379</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>136583210</v>
       </c>
       <c r="B69" t="n">
-        <v>100377</v>
+        <v>100379</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 29274-2026 artfynd.xlsx
+++ b/artfynd/A 29274-2026 artfynd.xlsx
@@ -1848,7 +1848,7 @@
         <v>136583208</v>
       </c>
       <c r="B12" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>136583209</v>
       </c>
       <c r="B68" t="n">
-        <v>100379</v>
+        <v>100385</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>136583210</v>
       </c>
       <c r="B69" t="n">
-        <v>100379</v>
+        <v>100385</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 29274-2026 artfynd.xlsx
+++ b/artfynd/A 29274-2026 artfynd.xlsx
@@ -1848,7 +1848,7 @@
         <v>136583208</v>
       </c>
       <c r="B12" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>136583209</v>
       </c>
       <c r="B68" t="n">
-        <v>100385</v>
+        <v>100387</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>136583210</v>
       </c>
       <c r="B69" t="n">
-        <v>100385</v>
+        <v>100387</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 29274-2026 artfynd.xlsx
+++ b/artfynd/A 29274-2026 artfynd.xlsx
@@ -1848,7 +1848,7 @@
         <v>136583208</v>
       </c>
       <c r="B12" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>136583209</v>
       </c>
       <c r="B68" t="n">
-        <v>100387</v>
+        <v>100388</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>136583210</v>
       </c>
       <c r="B69" t="n">
-        <v>100387</v>
+        <v>100388</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 29274-2026 artfynd.xlsx
+++ b/artfynd/A 29274-2026 artfynd.xlsx
@@ -1848,7 +1848,7 @@
         <v>136583208</v>
       </c>
       <c r="B12" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>136583209</v>
       </c>
       <c r="B68" t="n">
-        <v>100388</v>
+        <v>100394</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>136583210</v>
       </c>
       <c r="B69" t="n">
-        <v>100388</v>
+        <v>100394</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 29274-2026 artfynd.xlsx
+++ b/artfynd/A 29274-2026 artfynd.xlsx
@@ -1848,7 +1848,7 @@
         <v>136583208</v>
       </c>
       <c r="B12" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>136583209</v>
       </c>
       <c r="B68" t="n">
-        <v>100394</v>
+        <v>100398</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>136583210</v>
       </c>
       <c r="B69" t="n">
-        <v>100394</v>
+        <v>100398</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 29274-2026 artfynd.xlsx
+++ b/artfynd/A 29274-2026 artfynd.xlsx
@@ -8370,7 +8370,7 @@
         <v>136583209</v>
       </c>
       <c r="B68" t="n">
-        <v>100398</v>
+        <v>100400</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>136583210</v>
       </c>
       <c r="B69" t="n">
-        <v>100398</v>
+        <v>100400</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 29274-2026 artfynd.xlsx
+++ b/artfynd/A 29274-2026 artfynd.xlsx
@@ -1848,7 +1848,7 @@
         <v>136583208</v>
       </c>
       <c r="B12" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>136583209</v>
       </c>
       <c r="B68" t="n">
-        <v>100400</v>
+        <v>100402</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>136583210</v>
       </c>
       <c r="B69" t="n">
-        <v>100400</v>
+        <v>100402</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
